--- a/data/processed/harmonization/Carbon__Total_carbon/dois_filtering.xlsx
+++ b/data/processed/harmonization/Carbon__Total_carbon/dois_filtering.xlsx
@@ -2583,7 +2583,7 @@
         <v>185</v>
       </c>
       <c r="D53">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E53" t="s">
         <v>286</v>
